--- a/outputs/previsao_2026.xlsx
+++ b/outputs/previsao_2026.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47.2</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.9</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="8">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">

--- a/outputs/previsao_2026.xlsx
+++ b/outputs/previsao_2026.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -47,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,7 +433,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Previsao de votos validos (%)</t>
+          <t>Previsão de votos válidos (%)</t>
         </is>
       </c>
     </row>
@@ -445,7 +448,7 @@
           <t>Avante</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="1" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -460,7 +463,7 @@
           <t>DC</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -475,7 +478,7 @@
           <t>PCB</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -490,7 +493,7 @@
           <t>PL</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="1" t="n">
         <v>45.9</v>
       </c>
     </row>
@@ -505,7 +508,7 @@
           <t>PSTU</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -520,7 +523,7 @@
           <t>PT</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="1" t="n">
         <v>45.6</v>
       </c>
     </row>
@@ -535,7 +538,7 @@
           <t>Missão</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="1" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -550,7 +553,7 @@
           <t>PSD</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="1" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -565,7 +568,7 @@
           <t>Novo</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="1" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -580,7 +583,7 @@
           <t>PCO</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -595,7 +598,7 @@
           <t>UP</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -610,7 +613,7 @@
           <t>Democrata</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -621,7 +624,7 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
+      <c r="C14" s="1" t="n">
         <v>100</v>
       </c>
     </row>
@@ -647,17 +650,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Previsao (%)</t>
+          <t>Previsão (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abstencao</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+          <t>Abstenção</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>22.3</v>
       </c>
     </row>
@@ -667,7 +670,7 @@
           <t>Votos brancos</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="1" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -677,7 +680,7 @@
           <t>Votos nulos</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="1" t="n">
         <v>2.8</v>
       </c>
     </row>

--- a/outputs/previsao_2026.xlsx
+++ b/outputs/previsao_2026.xlsx
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45.9</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="6">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="8">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
